--- a/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
+++ b/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z159"/>
+  <dimension ref="A1:AB159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -655,6 +665,16 @@
           <t>030207</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>UGEL HUANCARAMA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -763,6 +783,16 @@
           <t>030204</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>UGEL HUANCARAMA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -871,6 +901,16 @@
           <t>030207</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>UGEL HUANCARAMA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -979,6 +1019,16 @@
           <t>030204</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>UGEL HUANCARAMA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1087,6 +1137,16 @@
           <t>030208</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>UGEL HUANCARAMA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1197,6 +1257,16 @@
       <c r="Z7" t="inlineStr">
         <is>
           <t>040520</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
         </is>
       </c>
     </row>
@@ -1307,6 +1377,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1415,6 +1495,16 @@
           <t>040108</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1527,6 +1617,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1637,6 +1737,16 @@
       <c r="Z11" t="inlineStr">
         <is>
           <t>040520</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
         </is>
       </c>
     </row>
@@ -1747,6 +1857,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1859,6 +1979,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1969,6 +2099,16 @@
       <c r="Z14" t="inlineStr">
         <is>
           <t>040520</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
         </is>
       </c>
     </row>
@@ -2079,6 +2219,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2187,6 +2337,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2295,6 +2455,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2403,6 +2573,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2511,6 +2691,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2623,6 +2813,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2733,6 +2933,16 @@
       <c r="Z21" t="inlineStr">
         <is>
           <t>040520</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
         </is>
       </c>
     </row>
@@ -2843,6 +3053,16 @@
           <t>040520</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2955,6 +3175,16 @@
           <t>050618</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3067,6 +3297,16 @@
           <t>050615</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3179,6 +3419,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3291,6 +3541,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3403,6 +3663,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3515,6 +3785,16 @@
           <t>050611</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3627,6 +3907,16 @@
           <t>050611</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3739,6 +4029,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3851,6 +4151,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3961,6 +4271,16 @@
       <c r="Z32" t="inlineStr">
         <is>
           <t>050619</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
         </is>
       </c>
     </row>
@@ -4059,6 +4379,8 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4171,6 +4493,16 @@
           <t>050611</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4283,6 +4615,16 @@
           <t>050407</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4395,6 +4737,16 @@
           <t>050204</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>UGEL CANGALLO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4507,6 +4859,16 @@
           <t>050203</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>UGEL CANGALLO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4619,6 +4981,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4731,6 +5103,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4843,6 +5225,16 @@
           <t>050203</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>UGEL CANGALLO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4955,6 +5347,16 @@
           <t>050601</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5067,6 +5469,16 @@
           <t>051007</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5179,6 +5591,16 @@
           <t>050105</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5291,6 +5713,16 @@
           <t>050205</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5403,6 +5835,16 @@
           <t>050102</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5515,6 +5957,16 @@
           <t>051012</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5627,6 +6079,16 @@
           <t>050106</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5739,6 +6201,16 @@
           <t>050106</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5851,6 +6323,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5963,6 +6445,16 @@
           <t>050109</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6075,6 +6567,16 @@
           <t>051012</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6187,6 +6689,16 @@
           <t>050107</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6299,6 +6811,16 @@
           <t>050205</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6411,6 +6933,16 @@
           <t>050205</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6523,6 +7055,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6635,6 +7177,16 @@
           <t>060204</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6747,6 +7299,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6859,6 +7421,16 @@
           <t>060204</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6971,6 +7543,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7083,6 +7665,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7195,6 +7787,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7307,6 +7909,16 @@
           <t>060201</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7419,6 +8031,16 @@
           <t>060203</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7531,6 +8153,16 @@
           <t>060203</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7643,6 +8275,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7755,6 +8397,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7867,6 +8519,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7979,6 +8641,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8091,6 +8763,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8203,6 +8885,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8315,6 +9007,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8427,6 +9129,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8541,6 +9253,16 @@
       <c r="Z73" t="inlineStr">
         <is>
           <t>060101</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
         </is>
       </c>
     </row>
@@ -8655,6 +9377,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8767,6 +9499,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8879,6 +9621,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8991,6 +9743,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9103,6 +9865,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9215,6 +9987,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9327,6 +10109,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9439,6 +10231,16 @@
           <t>060103</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9551,6 +10353,16 @@
           <t>060103</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9663,6 +10475,16 @@
           <t>060104</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9775,6 +10597,16 @@
           <t>060103</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9887,6 +10719,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9999,6 +10841,16 @@
           <t>060105</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10111,6 +10963,16 @@
           <t>060106</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10223,6 +11085,16 @@
           <t>060106</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10335,6 +11207,16 @@
           <t>060106</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10447,6 +11329,16 @@
           <t>060106</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10559,6 +11451,16 @@
           <t>060106</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10671,6 +11573,16 @@
           <t>060106</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10783,6 +11695,16 @@
           <t>060701</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>UGEL HUALGAYOC</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10895,6 +11817,16 @@
           <t>060111</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11007,6 +11939,16 @@
           <t>060111</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11115,6 +12057,16 @@
           <t>090704</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11223,6 +12175,16 @@
           <t>090704</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11331,6 +12293,16 @@
           <t>090703</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11439,6 +12411,16 @@
           <t>090703</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11547,6 +12529,16 @@
           <t>090706</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11655,6 +12647,16 @@
           <t>090711</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11763,6 +12765,16 @@
           <t>090711</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11871,6 +12883,16 @@
           <t>090704</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11979,6 +13001,16 @@
           <t>090704</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12087,6 +13119,16 @@
           <t>090706</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12195,6 +13237,16 @@
           <t>090706</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12303,6 +13355,16 @@
           <t>090706</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12411,6 +13473,16 @@
           <t>090706</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12519,6 +13591,16 @@
           <t>090706</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12627,6 +13709,16 @@
           <t>090711</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12739,6 +13831,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12845,6 +13947,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12951,6 +14063,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13045,6 +14167,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13151,6 +14283,16 @@
           <t>101005</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13257,6 +14399,16 @@
           <t>101005</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13363,6 +14515,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13469,6 +14631,16 @@
           <t>101001</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -13575,6 +14747,16 @@
           <t>101007</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -13683,6 +14865,16 @@
           <t>150404</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -13791,6 +14983,16 @@
           <t>150406</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -13899,6 +15101,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14007,6 +15219,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14115,6 +15337,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14223,6 +15455,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14331,6 +15573,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14439,6 +15691,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14547,6 +15809,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14655,6 +15927,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14763,6 +16045,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -14871,6 +16163,16 @@
           <t>100803</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14979,6 +16281,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15087,6 +16399,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15193,6 +16515,16 @@
       <c r="Z134" t="inlineStr">
         <is>
           <t>100801</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
         </is>
       </c>
     </row>
@@ -15273,6 +16605,8 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -15381,6 +16715,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15489,6 +16833,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15597,6 +16951,16 @@
           <t>100803</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15705,6 +17069,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15811,6 +17185,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15919,6 +17303,16 @@
           <t>100803</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16027,6 +17421,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16133,6 +17537,16 @@
       <c r="Z143" t="inlineStr">
         <is>
           <t>100803</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
         </is>
       </c>
     </row>
@@ -16213,6 +17627,8 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -16291,6 +17707,8 @@
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -16399,6 +17817,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -16507,6 +17935,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -16615,6 +18053,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -16723,6 +18171,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -16831,6 +18289,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -16939,6 +18407,16 @@
           <t>100803</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -17047,6 +18525,16 @@
           <t>100803</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -17155,6 +18643,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -17263,6 +18761,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -17371,6 +18879,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -17479,6 +18997,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -17587,6 +19115,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -17695,6 +19233,16 @@
           <t>100803</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -17801,6 +19349,16 @@
       <c r="Z159" t="inlineStr">
         <is>
           <t>100804</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
+++ b/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB159"/>
+  <dimension ref="A1:AC159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -675,6 +680,11 @@
           <t>UGEL HUANCARAMA</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -793,6 +803,11 @@
           <t>UGEL HUANCARAMA</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -911,6 +926,11 @@
           <t>UGEL HUANCARAMA</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1029,6 +1049,11 @@
           <t>UGEL HUANCARAMA</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1147,6 +1172,11 @@
           <t>UGEL HUANCARAMA</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1267,6 +1297,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>UGEL LA JOYA</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -1387,6 +1422,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1505,6 +1545,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1627,6 +1672,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1747,6 +1797,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>UGEL LA JOYA</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -1867,6 +1922,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1989,6 +2049,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2109,6 +2174,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>UGEL LA JOYA</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -2229,6 +2299,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2347,6 +2422,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2465,6 +2545,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2583,6 +2668,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2701,6 +2791,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2823,6 +2918,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2943,6 +3043,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>UGEL LA JOYA</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -3063,6 +3168,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3185,6 +3295,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3307,6 +3422,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3429,6 +3549,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3551,6 +3676,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3673,6 +3803,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3795,6 +3930,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3917,6 +4057,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4039,6 +4184,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4161,6 +4311,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4283,6 +4438,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4374,13 +4534,42 @@
           <t>112736</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>LUCANAS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>SANCOS</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>050619</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4503,6 +4692,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4625,6 +4819,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4747,6 +4946,11 @@
           <t>UGEL CANGALLO</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4869,6 +5073,11 @@
           <t>UGEL CANGALLO</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4991,6 +5200,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5113,6 +5327,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5235,6 +5454,11 @@
           <t>UGEL CANGALLO</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5357,6 +5581,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5479,6 +5708,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5601,6 +5835,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5723,6 +5962,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5845,6 +6089,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5967,6 +6216,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6089,6 +6343,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6211,6 +6470,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6333,6 +6597,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6455,6 +6724,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6577,6 +6851,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6699,6 +6978,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6821,6 +7105,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6943,6 +7232,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7065,6 +7359,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7187,6 +7486,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7309,6 +7613,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7431,6 +7740,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7553,6 +7867,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7675,6 +7994,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7797,6 +8121,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7919,6 +8248,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8041,6 +8375,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8163,6 +8502,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8285,6 +8629,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8407,6 +8756,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8529,6 +8883,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8651,6 +9010,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8773,6 +9137,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8895,6 +9264,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9017,6 +9391,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9139,6 +9518,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9263,6 +9647,11 @@
       <c r="AB73" t="inlineStr">
         <is>
           <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -9387,6 +9776,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9509,6 +9903,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9631,6 +10030,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9753,6 +10157,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9875,6 +10284,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9997,6 +10411,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10119,6 +10538,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10241,6 +10665,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10363,6 +10792,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10485,6 +10919,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10607,6 +11046,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10729,6 +11173,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10851,6 +11300,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10973,6 +11427,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11095,6 +11554,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11217,6 +11681,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11339,6 +11808,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11461,6 +11935,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11583,6 +12062,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11705,6 +12189,11 @@
           <t>UGEL HUALGAYOC</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11827,6 +12316,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11949,6 +12443,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12067,6 +12566,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12185,6 +12689,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12303,6 +12812,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12421,6 +12935,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12539,6 +13058,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12657,6 +13181,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12775,6 +13304,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12893,6 +13427,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13011,6 +13550,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13129,6 +13673,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13247,6 +13796,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13365,6 +13919,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13483,6 +14042,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13601,6 +14165,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13719,6 +14288,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13841,6 +14415,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13957,6 +14536,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14073,6 +14657,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14177,6 +14766,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14293,6 +14887,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14409,6 +15008,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14525,6 +15129,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14641,6 +15250,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14757,6 +15371,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14875,6 +15494,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14993,6 +15617,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15111,6 +15740,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15229,6 +15863,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15347,6 +15986,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15465,6 +16109,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15583,6 +16232,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15701,6 +16355,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15819,6 +16478,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15937,6 +16601,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16055,6 +16724,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -16173,6 +16847,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16291,6 +16970,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -16409,6 +17093,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16525,6 +17214,11 @@
       <c r="AB134" t="inlineStr">
         <is>
           <t>UGEL PACHITEA</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -16607,6 +17301,11 @@
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16725,6 +17424,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16843,6 +17547,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16961,6 +17670,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17079,6 +17793,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17195,6 +17914,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -17313,6 +18037,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17431,6 +18160,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17547,6 +18281,11 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>UGEL PACHITEA</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -17629,6 +18368,11 @@
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -17709,6 +18453,11 @@
       <c r="Z145" t="inlineStr"/>
       <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17827,6 +18576,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17945,6 +18699,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18063,6 +18822,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -18181,6 +18945,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -18299,6 +19068,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18417,6 +19191,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -18535,6 +19314,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -18653,6 +19437,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -18771,6 +19560,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -18889,6 +19683,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -19007,6 +19806,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -19125,6 +19929,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19243,6 +20052,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -19359,6 +20173,11 @@
       <c r="AB159" t="inlineStr">
         <is>
           <t>UGEL PACHITEA</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
+++ b/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC159"/>
+  <dimension ref="A1:AE159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,16 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -682,6 +692,16 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -805,6 +825,16 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>54711</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -928,6 +958,16 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>54102 ANTONIO BRACK</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1051,6 +1091,16 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>HATUN CHASKA</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1174,6 +1224,16 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>54140 JACINTO BENEGAS ORTIZ</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1300,6 +1360,16 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr">
+        <is>
+          <t>41502/41502/41502</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1424,6 +1494,16 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1547,6 +1627,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>LA JOYA/LA JOYA</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1674,6 +1764,16 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
+          <t>40661 ISABEL KRIEGER BEATO/40661 ISABEL KRIEGER BEATO/40661 ISABEL KRIEGER BEATO</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1800,6 +1900,16 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
+        <is>
+          <t>40097 REPUBLICA DE CANADA/40097 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1924,6 +2034,16 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
+          <t>JESUS EL BUEN PASTOR</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2051,6 +2171,16 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
+          <t>40655 NUESTRA SEÑORA DEL CARMEN/40655 NUESTRA SEÑORA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2177,6 +2307,16 @@
         </is>
       </c>
       <c r="AC14" t="inlineStr">
+        <is>
+          <t>ALMIRANTE MIGUEL GRAU/ALMIRANTE MIGUEL GRAU/ALMIRANTE MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2301,6 +2441,16 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>40284 PEDRO PAULET MOSTAJO</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2424,6 +2574,16 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>40284 PEDRO PAULET MOSTAJO</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2547,6 +2707,16 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
+          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2670,6 +2840,16 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
+          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2793,6 +2973,16 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
+          <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2920,6 +3110,16 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
+          <t>40666 ANTONIO RAYMONDI/40666 ANTONIO RAYMONDI</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3046,6 +3246,16 @@
         </is>
       </c>
       <c r="AC21" t="inlineStr">
+        <is>
+          <t>TUPAC AMARU II/TUPAC AMARU II</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3170,6 +3380,16 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
+          <t>40594 JUAN VELASCO A./40594 JUAN VELASCO A.</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3297,6 +3517,16 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
+          <t>22515</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3424,6 +3654,16 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
+          <t>24398 SAN MARTIN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3551,6 +3791,16 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
+          <t>24376</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3678,6 +3928,16 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
+          <t>24346</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3805,6 +4065,16 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
+          <t>24345</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3932,6 +4202,16 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
+          <t>24039</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4059,6 +4339,16 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
+          <t>24415</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4186,6 +4476,16 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4313,6 +4613,16 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4440,6 +4750,16 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
+          <t>PALCA</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4566,6 +4886,16 @@
         </is>
       </c>
       <c r="AC33" t="inlineStr">
+        <is>
+          <t>CHICALLY</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4694,6 +5024,16 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
+          <t>CCONTACC</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4821,6 +5161,16 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
+          <t>429-64</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4948,6 +5298,16 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
+          <t>38196</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5075,6 +5435,16 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
+          <t>38201</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5202,6 +5572,16 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
+          <t>24466</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5329,6 +5709,16 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
+          <t>24456</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5456,6 +5846,16 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
+          <t>414 - 51</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5583,6 +5983,16 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5710,6 +6120,16 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5837,6 +6257,16 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
+          <t>432-177</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5964,6 +6394,16 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
+          <t>414-50</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6091,6 +6531,16 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
+          <t>432-11</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6218,6 +6668,16 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
+          <t>430-03</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6345,6 +6805,16 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
+          <t>432-104</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6472,6 +6942,16 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
+          <t>432-109</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6599,6 +7079,16 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
+          <t>353/38056</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6726,6 +7216,16 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
+          <t>38760</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6853,6 +7353,16 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
+          <t>38538</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6980,6 +7490,16 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
+          <t>38341</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7107,6 +7627,16 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
+          <t>38206</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7234,6 +7764,16 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
+          <t>38986</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7361,6 +7901,16 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7488,6 +8038,16 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
+          <t>LUIS ALBERTO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7615,6 +8175,16 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
+          <t>821210</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7742,6 +8312,16 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
+          <t>82385</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7869,6 +8449,16 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7996,6 +8586,16 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8123,6 +8723,16 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
+          <t>821167</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8250,6 +8860,16 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
+          <t>821415</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8377,6 +8997,16 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8504,6 +9134,16 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
+          <t>MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8631,6 +9271,16 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
+          <t>82031</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8758,6 +9408,16 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
+          <t>FRAY ISACC SHAHUANO MURRIETA/FRAY ISACC SHAHUANO MURRIETA</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8885,6 +9545,16 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
+          <t>FRAY ISACC SHAHUANO MURRIETA/FRAY ISACC SHAHUANO MURRIETA</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9012,6 +9682,16 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9139,6 +9819,16 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
+          <t>82111</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9266,6 +9956,16 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
+          <t>82126/750/82126</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9393,6 +10093,16 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
+          <t>82126/750/82126</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9520,6 +10230,16 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
+          <t>82126/750/82126</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9650,6 +10370,16 @@
         </is>
       </c>
       <c r="AC73" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9778,6 +10508,16 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
+          <t>83005</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9905,6 +10645,16 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
+          <t>82122/82122/82122</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10032,6 +10782,16 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
+          <t>82122/82122/82122</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10159,6 +10919,16 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
+          <t>821021</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10286,6 +11056,16 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
+          <t>821006</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10413,6 +11193,16 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
+          <t>82020/82020</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10540,6 +11330,16 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
+          <t>82020/82020</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10667,6 +11467,16 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
+          <t>82147/849/82147</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10794,6 +11604,16 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
+          <t>82944</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -10921,6 +11741,16 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
+          <t>82142/82142</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11048,6 +11878,16 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11175,6 +12015,16 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
+          <t>821326</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11302,6 +12152,16 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
+          <t>821233</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11429,6 +12289,16 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
+          <t>82068/82068</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11556,6 +12426,16 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
+          <t>82068/82068</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11683,6 +12563,16 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11810,6 +12700,16 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
+          <t>821243</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -11937,6 +12837,16 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
+          <t>82065 PABLO ENRIQUE SANCHEZ ZEVALLOS</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12064,6 +12974,16 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
+          <t>INCA GARCILASO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12191,6 +13111,16 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12318,6 +13248,16 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
+          <t>CIRO ALEGRIA BAZAN</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12445,6 +13385,16 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12568,6 +13518,16 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12691,6 +13651,16 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12814,6 +13784,16 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -12937,6 +13917,16 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13060,6 +14050,16 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13183,6 +14183,16 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13306,6 +14316,16 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13429,6 +14449,16 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13552,6 +14582,16 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13675,6 +14715,16 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13798,6 +14848,16 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -13921,6 +14981,16 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14044,6 +15114,16 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
+          <t>31048</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14167,6 +15247,16 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14290,6 +15380,16 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14417,6 +15517,16 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
+          <t>32793/32793</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14538,6 +15648,16 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
+          <t>32793/32793</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14659,6 +15779,16 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
+          <t>32976/32976</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14768,6 +15898,16 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
+          <t>32976/32976</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -14889,6 +16029,16 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
+          <t>097</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15010,6 +16160,16 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
+          <t>32936/32936</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15131,6 +16291,16 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15252,6 +16422,16 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
+          <t>VIRGEN DE LA INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15373,6 +16553,16 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15496,6 +16686,16 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
+          <t>21004-1</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15619,6 +16819,16 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
+          <t>20305</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15742,6 +16952,16 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15865,6 +17085,16 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
+          <t>506-5 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -15988,6 +17218,16 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16111,6 +17351,16 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
+          <t>32715/32715/32715</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16234,6 +17484,16 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
+          <t>PUEBLO LIBRE</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16357,6 +17617,16 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
+          <t>PUEBLOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16480,6 +17750,16 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
+          <t>SANTA RITA BAJA</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16603,6 +17883,16 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16726,6 +18016,16 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
+          <t>32584</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16849,6 +18149,16 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
+          <t>32621/32621</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -16972,6 +18282,16 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -17095,6 +18415,16 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
+          <t>HUANIN</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -17217,6 +18547,16 @@
         </is>
       </c>
       <c r="AC134" t="inlineStr">
+        <is>
+          <t>32729</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -17294,14 +18634,28 @@
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
-      <c r="AB135" t="inlineStr"/>
-      <c r="AC135" t="inlineStr">
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>DRE HUÁNUCO</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -17426,6 +18780,16 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -17549,6 +18913,16 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
+          <t>33245/33245</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -17672,6 +19046,16 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
+          <t>LEONARDO DA VINCI</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -17795,6 +19179,16 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
+          <t>32579</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -17916,6 +19310,16 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
+          <t>GOYAR PUNTA/33301/33301</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -18039,6 +19443,16 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
+          <t>33393</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -18162,6 +19576,16 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
+          <t>JAVIER PULGAR VIDAL</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -18284,6 +19708,16 @@
         </is>
       </c>
       <c r="AC143" t="inlineStr">
+        <is>
+          <t>33234</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -18361,14 +19795,28 @@
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr"/>
-      <c r="AC144" t="inlineStr">
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>DRE HUÁNUCO</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -18446,14 +19894,28 @@
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
-      <c r="AB145" t="inlineStr"/>
-      <c r="AC145" t="inlineStr">
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>DRE HUÁNUCO</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -18578,6 +20040,16 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
+          <t>32605/32605</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -18701,6 +20173,16 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -18824,6 +20306,16 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
+          <t>32580/32580</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -18947,6 +20439,16 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19070,6 +20572,16 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
+          <t>AURAGSHAY</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19193,6 +20705,16 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
+          <t>32618/32618</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19316,6 +20838,16 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
+          <t>32817/32817/32817</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19439,6 +20971,16 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
+          <t>32908/32908</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19562,6 +21104,16 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
+          <t>32596</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19685,6 +21237,16 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
+          <t>32624/32624</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19808,6 +21370,16 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
+          <t>32769/32769</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -19931,6 +21503,16 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -20054,6 +21636,16 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -20176,6 +21768,16 @@
         </is>
       </c>
       <c r="AC159" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>

--- a/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
+++ b/output/bases_limpias/Grupo_07_SANEAMIENTO/df_digeged_sfl.xlsx
@@ -419,102 +419,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Codigo Modular</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AÑO</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DRE/GRE</t>
+          <t>dre_gre</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unidad Ejecutora</t>
+          <t>unidad_ejecutora</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>UGEL</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>producto</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Actividad</t>
+          <t>actividad</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Unidad de medida</t>
+          <t>unidad_de_medida</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Meta Fisica Programada (Cantidad)</t>
+          <t>meta_fisica_programada_cantidad</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Detalle de la Unidad de Medida (Nombre del Servicio contratado)</t>
+          <t>detalle_de_la_unidad_de_medida_nombre_del_servicio_contratad</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Centro Poblado</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Nivel</t>
+          <t>nivel</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>SIAGIE 2025</t>
+          <t>siagie_2025</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Intervención Culminada (Si/No)</t>
+          <t>intervencion_culminada_si_no</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>PIM 2025</t>
+          <t>pim_2025</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Fuentes de Financiamiento</t>
+          <t>fuentes_de_financiamiento</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>¿Como se ejecutaran los recursos asignados?</t>
+          <t>como_se_ejecutaran_los_recursos_asignados</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ETAPA</t>
+          <t>etapa</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FECHA DE INFORMACION</t>
+          <t>fecha_de_informacion</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>centro_poblado</t>
+          <t>centro_poblado_2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>ugel</t>
+          <t>ugel_2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
